--- a/Statistics/Tests/anova-test.xlsx
+++ b/Statistics/Tests/anova-test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sameen\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sameen\Data Science\Statistics\Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A64D51-DF11-434A-88FB-4099BF4B634E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D771835E-B7F4-4C11-B6E1-96019206D37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A7F85D02-F7FE-405F-A58A-92F2BE42A89F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
   <si>
     <t>ANOVA</t>
   </si>
@@ -193,6 +193,36 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <r>
+      <t>Parametric test</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = wo test jo data ke baare mein kuch assumptions maan ke chalta hai.</t>
+    </r>
+  </si>
+  <si>
+    <t>Main assumptions:</t>
+  </si>
+  <si>
+    <t>Data normally distributed ho (bell curve shape)</t>
+  </si>
+  <si>
+    <t>Groups ka variance lagbhag barabar ho</t>
+  </si>
+  <si>
+    <t>Data numeric ho (marks, cholesterol level, weight — na ke "yes/no" ya categories)</t>
+  </si>
+  <si>
+    <t>T-test, Z-test</t>
   </si>
 </sst>
 </file>
@@ -300,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -311,10 +341,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -779,19 +812,19 @@
       <c r="E12" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="K12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L12" s="10" t="s">
+      <c r="L12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="M12" s="10" t="s">
+      <c r="M12" s="9" t="s">
         <v>41</v>
       </c>
     </row>
@@ -805,19 +838,19 @@
       <c r="C13">
         <v>220</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13">
         <v>9</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13">
         <v>2380</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L13">
         <v>264.44444444444446</v>
       </c>
-      <c r="M13" s="8">
+      <c r="M13">
         <v>827.77777777778101</v>
       </c>
     </row>
@@ -831,19 +864,19 @@
       <c r="C14">
         <v>180</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14">
         <v>9</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14">
         <v>2170</v>
       </c>
-      <c r="L14" s="8">
+      <c r="L14">
         <v>241.11111111111111</v>
       </c>
-      <c r="M14" s="8">
+      <c r="M14">
         <v>511.11111111111103</v>
       </c>
     </row>
@@ -857,19 +890,19 @@
       <c r="C15">
         <v>230</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="8">
         <v>9</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="8">
         <v>1880</v>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="8">
         <v>208.88888888888889</v>
       </c>
-      <c r="M15" s="9">
+      <c r="M15" s="8">
         <v>411.11111111111109</v>
       </c>
     </row>
@@ -893,48 +926,48 @@
       <c r="A19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I19" s="10" t="s">
+      <c r="I19" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="J19" s="10" t="s">
+      <c r="J19" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="K19" s="10" t="s">
+      <c r="K19" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L19" s="10" t="s">
+      <c r="L19" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="M19" s="10" t="s">
+      <c r="M19" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="N19" s="10" t="s">
+      <c r="N19" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="O19" s="10" t="s">
+      <c r="O19" s="9" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="I20" s="8" t="s">
+      <c r="I20" t="s">
         <v>49</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J20">
         <v>14007.407407407405</v>
       </c>
-      <c r="K20" s="8">
+      <c r="K20">
         <v>2</v>
       </c>
-      <c r="L20" s="8">
+      <c r="L20">
         <v>7003.7037037037026</v>
       </c>
-      <c r="M20" s="8">
+      <c r="M20">
         <v>12.006349206349203</v>
       </c>
-      <c r="N20" s="8">
+      <c r="N20">
         <v>2.4336690651033204E-4</v>
       </c>
-      <c r="O20" s="8">
+      <c r="O20">
         <v>3.4028261053501945</v>
       </c>
     </row>
@@ -942,51 +975,41 @@
       <c r="A21" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I21" t="s">
         <v>50</v>
       </c>
-      <c r="J21" s="8">
+      <c r="J21">
         <v>14000</v>
       </c>
-      <c r="K21" s="8">
+      <c r="K21">
         <v>24</v>
       </c>
-      <c r="L21" s="8">
+      <c r="L21">
         <v>583.33333333333337</v>
       </c>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
     </row>
     <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>13</v>
       </c>
-      <c r="I23" s="9" t="s">
+      <c r="I23" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="8">
         <v>28007.407407407405</v>
       </c>
-      <c r="K23" s="9">
+      <c r="K23" s="8">
         <v>26</v>
       </c>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -1003,52 +1026,123 @@
         <v>16</v>
       </c>
     </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E30" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+    </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E32" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E33" s="11"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E34" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E35" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E36" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
+      <c r="K36" s="7"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E38" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F38" s="7"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="48" spans="1:1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>27</v>
       </c>
